--- a/ΕΝΗΜΕΡΩΤΙΚΑ_ΣΗΜΕΙΩΜΑΤΑ/2026-02/XLSX/ΕΝΗΜΕΡΩΤΙΚΟ_ΣΗΜΕΙΩΜΑ_ΣΗΘΥΑ_ΘΕΣΣΑΛΟΝΙΚΗΣ_2_ΜΟΝΟΠΡΟΣΩΠΗ_ΙΚΕ_2026-02.xlsx
+++ b/ΕΝΗΜΕΡΩΤΙΚΑ_ΣΗΜΕΙΩΜΑΤΑ/2026-02/XLSX/ΕΝΗΜΕΡΩΤΙΚΟ_ΣΗΜΕΙΩΜΑ_ΣΗΘΥΑ_ΘΕΣΣΑΛΟΝΙΚΗΣ_2_ΜΟΝΟΠΡΟΣΩΠΗ_ΙΚΕ_2026-02.xlsx
@@ -2844,7 +2844,7 @@
     <row r="6" ht="60.75" customFormat="1" customHeight="1" s="10">
       <c r="B6" s="80" t="inlineStr">
         <is>
-          <t>06/03/26</t>
+          <t>09/03/26</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -3196,13 +3196,13 @@
         <v>23326.8</v>
       </c>
       <c r="E23" s="25" t="n">
-        <v>87.50942040000001</v>
+        <v>1573.2722868</v>
       </c>
       <c r="F23" s="25" t="n">
         <v>5.83</v>
       </c>
       <c r="G23" s="92" t="n">
-        <v>3.75</v>
+        <v>67.44</v>
       </c>
       <c r="H23" s="93" t="n"/>
     </row>
@@ -3216,13 +3216,13 @@
         <v>17377.53</v>
       </c>
       <c r="E24" s="25" t="n">
-        <v>549.9405993</v>
+        <v>597.0373968</v>
       </c>
       <c r="F24" s="25" t="n">
         <v>4.34</v>
       </c>
       <c r="G24" s="92" t="n">
-        <v>31.65</v>
+        <v>34.36</v>
       </c>
       <c r="H24" s="93" t="n"/>
     </row>
@@ -3236,13 +3236,13 @@
         <v>18675.36</v>
       </c>
       <c r="E25" s="25" t="n">
-        <v>81.0330264</v>
+        <v>1670.981982</v>
       </c>
       <c r="F25" s="25" t="n">
         <v>4.67</v>
       </c>
       <c r="G25" s="92" t="n">
-        <v>4.34</v>
+        <v>89.48</v>
       </c>
       <c r="H25" s="93" t="n"/>
     </row>
@@ -3256,13 +3256,13 @@
         <v>21576.96</v>
       </c>
       <c r="E26" s="25" t="n">
-        <v>1227.9475878</v>
+        <v>1316.165007</v>
       </c>
       <c r="F26" s="25" t="n">
         <v>5.39</v>
       </c>
       <c r="G26" s="92" t="n">
-        <v>56.91</v>
+        <v>61</v>
       </c>
       <c r="H26" s="93" t="n"/>
     </row>
@@ -3416,13 +3416,13 @@
         <v>17057.61</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>87.964935</v>
+        <v>1279.3882266</v>
       </c>
       <c r="F34" s="25" t="n">
         <v>4.26</v>
       </c>
       <c r="G34" s="92" t="n">
-        <v>5.16</v>
+        <v>75</v>
       </c>
       <c r="H34" s="93" t="n"/>
     </row>
@@ -3436,13 +3436,13 @@
         <v>17485.41</v>
       </c>
       <c r="E35" s="25" t="n">
-        <v>1250.2390566</v>
+        <v>1338.2198709</v>
       </c>
       <c r="F35" s="25" t="n">
         <v>4.37</v>
       </c>
       <c r="G35" s="92" t="n">
-        <v>71.5</v>
+        <v>76.53</v>
       </c>
       <c r="H35" s="93" t="n"/>
     </row>
@@ -3456,13 +3456,13 @@
         <v>23334.93</v>
       </c>
       <c r="E36" s="25" t="n">
-        <v>75.4430847</v>
+        <v>1524.5875131</v>
       </c>
       <c r="F36" s="25" t="n">
         <v>5.83</v>
       </c>
       <c r="G36" s="92" t="n">
-        <v>3.23</v>
+        <v>65.33</v>
       </c>
       <c r="H36" s="93" t="n"/>
     </row>
@@ -3476,13 +3476,13 @@
         <v>18286.5</v>
       </c>
       <c r="E37" s="25" t="n">
-        <v>0</v>
+        <v>1264.6201287</v>
       </c>
       <c r="F37" s="25" t="n">
         <v>4.57</v>
       </c>
       <c r="G37" s="92" t="n">
-        <v>0</v>
+        <v>69.16</v>
       </c>
       <c r="H37" s="93" t="n"/>
     </row>
@@ -3496,13 +3496,13 @@
         <v>567082.14</v>
       </c>
       <c r="E38" s="95" t="n">
-        <v>43096.25</v>
+        <v>50300.45</v>
       </c>
       <c r="F38" s="95" t="n">
         <v>141.74</v>
       </c>
       <c r="G38" s="96" t="n">
-        <v>76</v>
+        <v>88.7</v>
       </c>
       <c r="H38" s="93" t="n"/>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="G46" s="83" t="n"/>
       <c r="H46" s="105" t="n">
-        <v>43096.25</v>
+        <v>50300.45</v>
       </c>
       <c r="I46" s="45" t="n"/>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="C53" s="110" t="inlineStr">
         <is>
-          <t>08/03/26</t>
+          <t>11/03/26</t>
         </is>
       </c>
       <c r="D53" s="111" t="n"/>
